--- a/Project 4 - Gantt Chart.xlsx
+++ b/Project 4 - Gantt Chart.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30015"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uofnebraska-my.sharepoint.com/personal/64147067_nebraska_edu/Documents/UNO/Engineer/CIVE 202/Lab 4/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uofnebraska-my.sharepoint.com/personal/67761206_nebraska_edu/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CF843B92-6C61-422D-8139-5452D5BEEBD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="231" documentId="11_3C4179B01545E19DD6C385890107473B0B440F85" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55308B3E-8D32-41BD-8956-4C492C233DA1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -90,10 +90,22 @@
     <t>Team A</t>
   </si>
   <si>
+    <t>Download SVI and Census Tract datasets</t>
+  </si>
+  <si>
+    <t>Noah Morland</t>
+  </si>
+  <si>
     <t>Clean and Merge Data</t>
   </si>
   <si>
+    <t>Rashid Hamid</t>
+  </si>
+  <si>
     <t>Create New Columns for New Risk Definition</t>
+  </si>
+  <si>
+    <t>Mehgan Paulino-Alejandro</t>
   </si>
   <si>
     <t xml:space="preserve">Handle missing or NA values in the dataset </t>
@@ -193,18 +205,6 @@
   <si>
     <t>Businesses will find invoices, time sheets, inventory trackers, financial statements, and project planning templates. Teachers and students will find resources such as class schedules, grade books, and attendance sheets. Organize your family life with meal planners, checklists, and exercise logs. Each template is thoroughly researched, refined, and improved over time through feedback from thousands of users.</t>
   </si>
-  <si>
-    <t>Download SVI and Census Tract datasets</t>
-  </si>
-  <si>
-    <t>Mehgan Paulino-Alejandro</t>
-  </si>
-  <si>
-    <t>Rashid Hamid</t>
-  </si>
-  <si>
-    <t>Noah Morland</t>
-  </si>
 </sst>
 </file>
 
@@ -217,7 +217,7 @@
     <numFmt numFmtId="166" formatCode="mmm\ d\,\ yyyy"/>
     <numFmt numFmtId="167" formatCode="d"/>
   </numFmts>
-  <fonts count="32" x14ac:knownFonts="1">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1091,6 +1091,27 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
+    <xf numFmtId="166" fontId="19" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="27" fillId="0" borderId="0" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1103,30 +1124,9 @@
     <xf numFmtId="0" fontId="20" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="27" fillId="0" borderId="0" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="19" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="19" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="19" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="13">
     <cellStyle name="Comma" xfId="4" builtinId="3" customBuiltin="1"/>
@@ -2237,20 +2237,20 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BL36"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="30" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="2.69921875" style="13" customWidth="1"/>
-    <col min="2" max="2" width="51.09765625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.69921875" customWidth="1"/>
-    <col min="4" max="4" width="10.69921875" customWidth="1"/>
-    <col min="5" max="5" width="10.69921875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="10.69921875" customWidth="1"/>
-    <col min="7" max="7" width="2.69921875" customWidth="1"/>
+    <col min="1" max="1" width="2.75" style="13" customWidth="1"/>
+    <col min="2" max="2" width="51.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.75" customWidth="1"/>
+    <col min="4" max="4" width="10.75" customWidth="1"/>
+    <col min="5" max="5" width="10.75" style="2" customWidth="1"/>
+    <col min="6" max="6" width="10.75" customWidth="1"/>
+    <col min="7" max="7" width="2.75" customWidth="1"/>
     <col min="8" max="8" width="6" hidden="1" customWidth="1"/>
-    <col min="9" max="65" width="2.69921875" customWidth="1"/>
+    <col min="9" max="65" width="2.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:64" ht="90" customHeight="1" x14ac:dyDescent="1.45">
+    <row r="1" spans="1:64" ht="90" customHeight="1">
       <c r="A1" s="14"/>
       <c r="B1" s="97" t="s">
         <v>0</v>
@@ -2260,59 +2260,59 @@
       <c r="E1" s="20"/>
       <c r="F1" s="21"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="114" t="s">
+      <c r="I1" s="111" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
       <c r="P1" s="24"/>
-      <c r="Q1" s="113">
+      <c r="Q1" s="110">
         <v>46115</v>
       </c>
-      <c r="R1" s="112"/>
-      <c r="S1" s="112"/>
-      <c r="T1" s="112"/>
-      <c r="U1" s="112"/>
-      <c r="V1" s="112"/>
-      <c r="W1" s="112"/>
-      <c r="X1" s="112"/>
-      <c r="Y1" s="112"/>
-      <c r="Z1" s="112"/>
-    </row>
-    <row r="2" spans="1:64" ht="30" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+    </row>
+    <row r="2" spans="1:64" ht="30" customHeight="1">
       <c r="B2" s="95"/>
       <c r="C2" s="96"/>
       <c r="D2" s="22"/>
       <c r="E2" s="23"/>
       <c r="F2" s="22"/>
-      <c r="I2" s="114" t="s">
+      <c r="I2" s="111" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="115"/>
-      <c r="K2" s="115"/>
-      <c r="L2" s="115"/>
-      <c r="M2" s="115"/>
-      <c r="N2" s="115"/>
-      <c r="O2" s="115"/>
+      <c r="J2" s="116"/>
+      <c r="K2" s="116"/>
+      <c r="L2" s="116"/>
+      <c r="M2" s="116"/>
+      <c r="N2" s="116"/>
+      <c r="O2" s="116"/>
       <c r="P2" s="24"/>
-      <c r="Q2" s="111">
+      <c r="Q2" s="109">
         <v>1</v>
       </c>
-      <c r="R2" s="112"/>
-      <c r="S2" s="112"/>
-      <c r="T2" s="112"/>
-      <c r="U2" s="112"/>
-      <c r="V2" s="112"/>
-      <c r="W2" s="112"/>
-      <c r="X2" s="112"/>
-      <c r="Y2" s="112"/>
-      <c r="Z2" s="112"/>
-    </row>
-    <row r="3" spans="1:64" s="26" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R2" s="117"/>
+      <c r="S2" s="117"/>
+      <c r="T2" s="117"/>
+      <c r="U2" s="117"/>
+      <c r="V2" s="117"/>
+      <c r="W2" s="117"/>
+      <c r="X2" s="117"/>
+      <c r="Y2" s="117"/>
+      <c r="Z2" s="117"/>
+    </row>
+    <row r="3" spans="1:64" s="26" customFormat="1" ht="30" customHeight="1">
       <c r="A3" s="13"/>
       <c r="B3" s="25" t="s">
         <v>3</v>
@@ -2320,108 +2320,108 @@
       <c r="D3" s="27"/>
       <c r="E3" s="28"/>
     </row>
-    <row r="4" spans="1:64" s="26" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:64" s="26" customFormat="1" ht="30" customHeight="1">
       <c r="A4" s="14"/>
       <c r="B4" s="29" t="s">
         <v>4</v>
       </c>
       <c r="E4" s="30"/>
-      <c r="I4" s="118">
+      <c r="I4" s="107">
         <f>I5</f>
         <v>46111</v>
       </c>
-      <c r="J4" s="116"/>
-      <c r="K4" s="116"/>
-      <c r="L4" s="116"/>
-      <c r="M4" s="116"/>
-      <c r="N4" s="116"/>
-      <c r="O4" s="116"/>
-      <c r="P4" s="116">
+      <c r="J4" s="105"/>
+      <c r="K4" s="105"/>
+      <c r="L4" s="105"/>
+      <c r="M4" s="105"/>
+      <c r="N4" s="105"/>
+      <c r="O4" s="105"/>
+      <c r="P4" s="105">
         <f>P5</f>
         <v>46118</v>
       </c>
-      <c r="Q4" s="116"/>
-      <c r="R4" s="116"/>
-      <c r="S4" s="116"/>
-      <c r="T4" s="116"/>
-      <c r="U4" s="116"/>
-      <c r="V4" s="116"/>
-      <c r="W4" s="116">
+      <c r="Q4" s="105"/>
+      <c r="R4" s="105"/>
+      <c r="S4" s="105"/>
+      <c r="T4" s="105"/>
+      <c r="U4" s="105"/>
+      <c r="V4" s="105"/>
+      <c r="W4" s="105">
         <f>W5</f>
         <v>46125</v>
       </c>
-      <c r="X4" s="116"/>
-      <c r="Y4" s="116"/>
-      <c r="Z4" s="116"/>
-      <c r="AA4" s="116"/>
-      <c r="AB4" s="116"/>
-      <c r="AC4" s="116"/>
-      <c r="AD4" s="116">
+      <c r="X4" s="105"/>
+      <c r="Y4" s="105"/>
+      <c r="Z4" s="105"/>
+      <c r="AA4" s="105"/>
+      <c r="AB4" s="105"/>
+      <c r="AC4" s="105"/>
+      <c r="AD4" s="105">
         <f>AD5</f>
         <v>46132</v>
       </c>
-      <c r="AE4" s="116"/>
-      <c r="AF4" s="116"/>
-      <c r="AG4" s="116"/>
-      <c r="AH4" s="116"/>
-      <c r="AI4" s="116"/>
-      <c r="AJ4" s="116"/>
-      <c r="AK4" s="116">
+      <c r="AE4" s="105"/>
+      <c r="AF4" s="105"/>
+      <c r="AG4" s="105"/>
+      <c r="AH4" s="105"/>
+      <c r="AI4" s="105"/>
+      <c r="AJ4" s="105"/>
+      <c r="AK4" s="105">
         <f>AK5</f>
         <v>46139</v>
       </c>
-      <c r="AL4" s="116"/>
-      <c r="AM4" s="116"/>
-      <c r="AN4" s="116"/>
-      <c r="AO4" s="116"/>
-      <c r="AP4" s="116"/>
-      <c r="AQ4" s="116"/>
-      <c r="AR4" s="116">
+      <c r="AL4" s="105"/>
+      <c r="AM4" s="105"/>
+      <c r="AN4" s="105"/>
+      <c r="AO4" s="105"/>
+      <c r="AP4" s="105"/>
+      <c r="AQ4" s="105"/>
+      <c r="AR4" s="105">
         <f>AR5</f>
         <v>46146</v>
       </c>
-      <c r="AS4" s="116"/>
-      <c r="AT4" s="116"/>
-      <c r="AU4" s="116"/>
-      <c r="AV4" s="116"/>
-      <c r="AW4" s="116"/>
-      <c r="AX4" s="116"/>
-      <c r="AY4" s="116">
+      <c r="AS4" s="105"/>
+      <c r="AT4" s="105"/>
+      <c r="AU4" s="105"/>
+      <c r="AV4" s="105"/>
+      <c r="AW4" s="105"/>
+      <c r="AX4" s="105"/>
+      <c r="AY4" s="105">
         <f>AY5</f>
         <v>46153</v>
       </c>
-      <c r="AZ4" s="116"/>
-      <c r="BA4" s="116"/>
-      <c r="BB4" s="116"/>
-      <c r="BC4" s="116"/>
-      <c r="BD4" s="116"/>
-      <c r="BE4" s="116"/>
-      <c r="BF4" s="116">
+      <c r="AZ4" s="105"/>
+      <c r="BA4" s="105"/>
+      <c r="BB4" s="105"/>
+      <c r="BC4" s="105"/>
+      <c r="BD4" s="105"/>
+      <c r="BE4" s="105"/>
+      <c r="BF4" s="105">
         <f>BF5</f>
         <v>46160</v>
       </c>
-      <c r="BG4" s="116"/>
-      <c r="BH4" s="116"/>
-      <c r="BI4" s="116"/>
-      <c r="BJ4" s="116"/>
-      <c r="BK4" s="116"/>
-      <c r="BL4" s="117"/>
-    </row>
-    <row r="5" spans="1:64" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="105"/>
-      <c r="B5" s="106" t="s">
+      <c r="BG4" s="105"/>
+      <c r="BH4" s="105"/>
+      <c r="BI4" s="105"/>
+      <c r="BJ4" s="105"/>
+      <c r="BK4" s="105"/>
+      <c r="BL4" s="106"/>
+    </row>
+    <row r="5" spans="1:64" s="26" customFormat="1" ht="15" customHeight="1">
+      <c r="A5" s="112"/>
+      <c r="B5" s="113" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="108" t="s">
+      <c r="C5" s="115" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="110" t="s">
+      <c r="D5" s="108" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="110" t="s">
+      <c r="E5" s="108" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="110" t="s">
+      <c r="F5" s="108" t="s">
         <v>9</v>
       </c>
       <c r="I5" s="31">
@@ -2649,13 +2649,13 @@
         <v>46166</v>
       </c>
     </row>
-    <row r="6" spans="1:64" s="26" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="105"/>
-      <c r="B6" s="107"/>
-      <c r="C6" s="109"/>
-      <c r="D6" s="109"/>
-      <c r="E6" s="109"/>
-      <c r="F6" s="109"/>
+    <row r="6" spans="1:64" s="26" customFormat="1" ht="15" customHeight="1" thickBot="1">
+      <c r="A6" s="112"/>
+      <c r="B6" s="114"/>
+      <c r="C6" s="118"/>
+      <c r="D6" s="118"/>
+      <c r="E6" s="118"/>
+      <c r="F6" s="118"/>
       <c r="I6" s="34" t="str">
         <f t="shared" ref="I6:AN6" si="3">LEFT(TEXT(I5,"ddd"),1)</f>
         <v>M</v>
@@ -2881,7 +2881,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="7" spans="1:64" s="26" customFormat="1" ht="30" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:64" s="26" customFormat="1" ht="30" hidden="1" customHeight="1" thickBot="1">
       <c r="A7" s="13" t="s">
         <v>10</v>
       </c>
@@ -2891,7 +2891,7 @@
       <c r="E7" s="37"/>
       <c r="F7" s="37"/>
       <c r="H7" s="26" t="str">
-        <f>IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
+        <f ca="1">IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
         <v/>
       </c>
       <c r="I7" s="39"/>
@@ -2951,7 +2951,7 @@
       <c r="BK7" s="39"/>
       <c r="BL7" s="39"/>
     </row>
-    <row r="8" spans="1:64" s="46" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:64" s="46" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A8" s="14"/>
       <c r="B8" s="40" t="s">
         <v>11</v>
@@ -2962,7 +2962,7 @@
       <c r="F8" s="44"/>
       <c r="G8" s="17"/>
       <c r="H8" s="5" t="str">
-        <f t="shared" ref="H8:H33" si="5">IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
+        <f t="shared" ref="H8:H33" ca="1" si="5">IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
         <v/>
       </c>
       <c r="I8" s="45"/>
@@ -3022,7 +3022,7 @@
       <c r="BK8" s="45"/>
       <c r="BL8" s="45"/>
     </row>
-    <row r="9" spans="1:64" s="46" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:64" s="46" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A9" s="14"/>
       <c r="B9" s="47" t="s">
         <v>12</v>
@@ -3043,7 +3043,7 @@
       </c>
       <c r="G9" s="17"/>
       <c r="H9" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" ca="1" si="5"/>
         <v>3</v>
       </c>
       <c r="I9" s="50"/>
@@ -3103,13 +3103,13 @@
       <c r="BK9" s="50"/>
       <c r="BL9" s="50"/>
     </row>
-    <row r="10" spans="1:64" s="46" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:64" s="46" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A10" s="14"/>
       <c r="B10" s="51" t="s">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="C10" s="52" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="D10" s="53">
         <v>1</v>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="G10" s="17"/>
       <c r="H10" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" ca="1" si="5"/>
         <v>3</v>
       </c>
       <c r="I10" s="50"/>
@@ -3184,13 +3184,13 @@
       <c r="BK10" s="50"/>
       <c r="BL10" s="50"/>
     </row>
-    <row r="11" spans="1:64" s="46" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:64" s="46" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A11" s="13"/>
       <c r="B11" s="51" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C11" s="52" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="D11" s="53">
         <v>1</v>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="G11" s="17"/>
       <c r="H11" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" ca="1" si="5"/>
         <v>3</v>
       </c>
       <c r="I11" s="50"/>
@@ -3265,13 +3265,13 @@
       <c r="BK11" s="50"/>
       <c r="BL11" s="50"/>
     </row>
-    <row r="12" spans="1:64" s="46" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:64" s="46" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A12" s="13"/>
       <c r="B12" s="51" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C12" s="52" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="D12" s="53">
         <v>1</v>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="G12" s="17"/>
       <c r="H12" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" ca="1" si="5"/>
         <v>3</v>
       </c>
       <c r="I12" s="50"/>
@@ -3346,13 +3346,13 @@
       <c r="BK12" s="50"/>
       <c r="BL12" s="50"/>
     </row>
-    <row r="13" spans="1:64" s="46" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:64" s="46" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A13" s="13"/>
       <c r="B13" s="51" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C13" s="52" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="D13" s="53">
         <v>1</v>
@@ -3367,7 +3367,7 @@
       </c>
       <c r="G13" s="17"/>
       <c r="H13" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" ca="1" si="5"/>
         <v>6</v>
       </c>
       <c r="I13" s="50"/>
@@ -3427,10 +3427,10 @@
       <c r="BK13" s="50"/>
       <c r="BL13" s="50"/>
     </row>
-    <row r="14" spans="1:64" s="46" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:64" s="46" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A14" s="14"/>
       <c r="B14" s="56" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C14" s="57"/>
       <c r="D14" s="58"/>
@@ -3438,17 +3438,17 @@
       <c r="F14" s="60"/>
       <c r="G14" s="17"/>
       <c r="H14" s="5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:64" s="46" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:64" s="46" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A15" s="14"/>
       <c r="B15" s="61" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C15" s="62" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="D15" s="63">
         <v>1</v>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="G15" s="17"/>
       <c r="H15" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" ca="1" si="5"/>
         <v>5</v>
       </c>
       <c r="I15" s="50"/>
@@ -3523,13 +3523,13 @@
       <c r="BK15" s="50"/>
       <c r="BL15" s="50"/>
     </row>
-    <row r="16" spans="1:64" s="46" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:64" s="46" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A16" s="13"/>
       <c r="B16" s="61" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C16" s="62" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="D16" s="63">
         <v>1</v>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="G16" s="17"/>
       <c r="H16" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" ca="1" si="5"/>
         <v>8</v>
       </c>
       <c r="I16" s="50"/>
@@ -3604,13 +3604,13 @@
       <c r="BK16" s="50"/>
       <c r="BL16" s="50"/>
     </row>
-    <row r="17" spans="1:64" s="46" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:64" s="46" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A17" s="13"/>
       <c r="B17" s="61" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C17" s="62" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="D17" s="63">
         <v>1</v>
@@ -3625,7 +3625,7 @@
       </c>
       <c r="G17" s="17"/>
       <c r="H17" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" ca="1" si="5"/>
         <v>3</v>
       </c>
       <c r="I17" s="50"/>
@@ -3685,13 +3685,13 @@
       <c r="BK17" s="50"/>
       <c r="BL17" s="50"/>
     </row>
-    <row r="18" spans="1:64" s="46" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:64" s="46" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A18" s="13"/>
       <c r="B18" s="61" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C18" s="62" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="D18" s="63">
         <v>1</v>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="G18" s="17"/>
       <c r="H18" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" ca="1" si="5"/>
         <v>3</v>
       </c>
       <c r="I18" s="50"/>
@@ -3766,7 +3766,7 @@
       <c r="BK18" s="50"/>
       <c r="BL18" s="50"/>
     </row>
-    <row r="19" spans="1:64" s="46" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:64" s="46" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A19" s="13"/>
       <c r="B19" s="61"/>
       <c r="C19" s="62"/>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="G19" s="17"/>
       <c r="H19" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" ca="1" si="5"/>
         <v>4</v>
       </c>
       <c r="I19" s="50"/>
@@ -3841,10 +3841,10 @@
       <c r="BK19" s="50"/>
       <c r="BL19" s="50"/>
     </row>
-    <row r="20" spans="1:64" s="46" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:64" s="46" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A20" s="13"/>
       <c r="B20" s="65" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C20" s="66"/>
       <c r="D20" s="67"/>
@@ -3852,7 +3852,7 @@
       <c r="F20" s="69"/>
       <c r="G20" s="17"/>
       <c r="H20" s="5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="I20" s="70"/>
@@ -3912,13 +3912,13 @@
       <c r="BK20" s="70"/>
       <c r="BL20" s="70"/>
     </row>
-    <row r="21" spans="1:64" s="46" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:64" s="46" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A21" s="13"/>
       <c r="B21" s="71" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C21" s="72" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="D21" s="73">
         <v>1</v>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="G21" s="17"/>
       <c r="H21" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" ca="1" si="5"/>
         <v>3</v>
       </c>
       <c r="I21" s="50"/>
@@ -3993,13 +3993,13 @@
       <c r="BK21" s="50"/>
       <c r="BL21" s="50"/>
     </row>
-    <row r="22" spans="1:64" s="46" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:64" s="46" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A22" s="13"/>
       <c r="B22" s="71" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C22" s="72" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="D22" s="73">
         <v>1</v>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="G22" s="17"/>
       <c r="H22" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" ca="1" si="5"/>
         <v>4</v>
       </c>
       <c r="I22" s="50"/>
@@ -4074,13 +4074,13 @@
       <c r="BK22" s="50"/>
       <c r="BL22" s="50"/>
     </row>
-    <row r="23" spans="1:64" s="46" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:64" s="46" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A23" s="13"/>
       <c r="B23" s="71" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C23" s="72" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="D23" s="73">
         <v>1</v>
@@ -4095,7 +4095,7 @@
       </c>
       <c r="G23" s="17"/>
       <c r="H23" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" ca="1" si="5"/>
         <v>2</v>
       </c>
       <c r="I23" s="50"/>
@@ -4155,13 +4155,13 @@
       <c r="BK23" s="50"/>
       <c r="BL23" s="50"/>
     </row>
-    <row r="24" spans="1:64" s="46" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:64" s="46" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A24" s="13"/>
       <c r="B24" s="71" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C24" s="72" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="D24" s="73">
         <v>1</v>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="G24" s="17"/>
       <c r="H24" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" ca="1" si="5"/>
         <v>19</v>
       </c>
       <c r="I24" s="50"/>
@@ -4236,13 +4236,13 @@
       <c r="BK24" s="50"/>
       <c r="BL24" s="50"/>
     </row>
-    <row r="25" spans="1:64" s="46" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:64" s="46" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A25" s="13"/>
       <c r="B25" s="71" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C25" s="72" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="D25" s="73">
         <v>1</v>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="G25" s="17"/>
       <c r="H25" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" ca="1" si="5"/>
         <v>4</v>
       </c>
       <c r="I25" s="50"/>
@@ -4317,10 +4317,10 @@
       <c r="BK25" s="50"/>
       <c r="BL25" s="50"/>
     </row>
-    <row r="26" spans="1:64" s="46" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:64" s="46" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A26" s="13"/>
       <c r="B26" s="75" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C26" s="76"/>
       <c r="D26" s="77"/>
@@ -4328,7 +4328,7 @@
       <c r="F26" s="79"/>
       <c r="G26" s="17"/>
       <c r="H26" s="5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="I26" s="80"/>
@@ -4388,13 +4388,13 @@
       <c r="BK26" s="80"/>
       <c r="BL26" s="80"/>
     </row>
-    <row r="27" spans="1:64" s="46" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:64" s="46" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A27" s="13"/>
       <c r="B27" s="81" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C27" s="82" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="D27" s="83">
         <v>1</v>
@@ -4404,13 +4404,13 @@
         <v>46132</v>
       </c>
       <c r="F27" s="84">
-        <f>E27+2</f>
-        <v>46134</v>
+        <f>E27+1</f>
+        <v>46133</v>
       </c>
       <c r="G27" s="17"/>
       <c r="H27" s="5">
-        <f t="shared" si="5"/>
-        <v>3</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>2</v>
       </c>
       <c r="I27" s="50"/>
       <c r="J27" s="50"/>
@@ -4469,13 +4469,13 @@
       <c r="BK27" s="50"/>
       <c r="BL27" s="50"/>
     </row>
-    <row r="28" spans="1:64" s="46" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:64" s="46" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A28" s="13"/>
       <c r="B28" s="81" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C28" s="82" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="D28" s="83">
         <v>1</v>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="G28" s="17"/>
       <c r="H28" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
       <c r="I28" s="50"/>
@@ -4550,10 +4550,10 @@
       <c r="BK28" s="50"/>
       <c r="BL28" s="50"/>
     </row>
-    <row r="29" spans="1:64" s="46" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:64" s="46" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A29" s="13"/>
       <c r="B29" s="81" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C29" s="82" t="s">
         <v>13</v>
@@ -4571,7 +4571,7 @@
       </c>
       <c r="G29" s="17"/>
       <c r="H29" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" ca="1" si="5"/>
         <v>4</v>
       </c>
       <c r="I29" s="50"/>
@@ -4631,13 +4631,13 @@
       <c r="BK29" s="50"/>
       <c r="BL29" s="50"/>
     </row>
-    <row r="30" spans="1:64" s="46" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:64" s="46" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A30" s="13"/>
       <c r="B30" s="81" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C30" s="82" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="D30" s="83">
         <v>1</v>
@@ -4652,7 +4652,7 @@
       </c>
       <c r="G30" s="17"/>
       <c r="H30" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" ca="1" si="5"/>
         <v>4</v>
       </c>
       <c r="I30" s="50"/>
@@ -4712,7 +4712,7 @@
       <c r="BK30" s="50"/>
       <c r="BL30" s="50"/>
     </row>
-    <row r="31" spans="1:64" s="46" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:64" s="46" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A31" s="13"/>
       <c r="B31" s="81"/>
       <c r="C31" s="82"/>
@@ -4721,7 +4721,7 @@
       <c r="F31" s="84"/>
       <c r="G31" s="17"/>
       <c r="H31" s="5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="I31" s="50"/>
@@ -4781,7 +4781,7 @@
       <c r="BK31" s="50"/>
       <c r="BL31" s="50"/>
     </row>
-    <row r="32" spans="1:64" s="46" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:64" s="46" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A32" s="13"/>
       <c r="B32" s="85"/>
       <c r="C32" s="86"/>
@@ -4790,7 +4790,7 @@
       <c r="F32" s="88"/>
       <c r="G32" s="17"/>
       <c r="H32" s="5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="I32" s="45"/>
@@ -4850,10 +4850,10 @@
       <c r="BK32" s="45"/>
       <c r="BL32" s="45"/>
     </row>
-    <row r="33" spans="1:64" s="46" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:64" s="46" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A33" s="14"/>
       <c r="B33" s="89" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C33" s="90"/>
       <c r="D33" s="91"/>
@@ -4861,7 +4861,7 @@
       <c r="F33" s="93"/>
       <c r="G33" s="17"/>
       <c r="H33" s="6" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="I33" s="94"/>
@@ -4921,18 +4921,28 @@
       <c r="BK33" s="94"/>
       <c r="BL33" s="94"/>
     </row>
-    <row r="34" spans="1:64" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:64" ht="30" customHeight="1">
       <c r="G34" s="3"/>
     </row>
-    <row r="35" spans="1:64" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:64" ht="30" customHeight="1">
       <c r="C35" s="16"/>
       <c r="F35" s="15"/>
     </row>
-    <row r="36" spans="1:64" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:64" ht="30" customHeight="1">
       <c r="C36" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="Q2:Z2"/>
+    <mergeCell ref="Q1:Z1"/>
+    <mergeCell ref="I1:O1"/>
+    <mergeCell ref="I2:O2"/>
     <mergeCell ref="BF4:BL4"/>
     <mergeCell ref="I4:O4"/>
     <mergeCell ref="P4:V4"/>
@@ -4941,16 +4951,6 @@
     <mergeCell ref="AK4:AQ4"/>
     <mergeCell ref="AR4:AX4"/>
     <mergeCell ref="AY4:BE4"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="Q2:Z2"/>
-    <mergeCell ref="Q1:Z1"/>
-    <mergeCell ref="I1:O1"/>
-    <mergeCell ref="I2:O2"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
   </mergeCells>
   <conditionalFormatting sqref="D7:D33">
     <cfRule type="dataBar" priority="23">
@@ -5061,110 +5061,110 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.15"/>
   <cols>
     <col min="1" max="1" width="87" style="7" customWidth="1"/>
     <col min="2" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="46.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="1:2" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="46.5" customHeight="1"/>
+    <row r="2" spans="1:2" s="9" customFormat="1" ht="15.6">
       <c r="A2" s="98" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="8"/>
     </row>
-    <row r="3" spans="1:2" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A3" s="99"/>
       <c r="B3" s="12"/>
     </row>
-    <row r="4" spans="1:2" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.7">
+    <row r="4" spans="1:2" s="10" customFormat="1" ht="30">
       <c r="A4" s="100" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="74.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="74.25" customHeight="1">
       <c r="A5" s="101" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="26.25" customHeight="1">
       <c r="A6" s="100" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" s="7" customFormat="1" ht="205.2" customHeight="1" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" s="7" customFormat="1" ht="205.15" customHeight="1">
       <c r="A7" s="102" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.7">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" s="10" customFormat="1" ht="30">
       <c r="A8" s="100" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="41.4" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="41.45">
       <c r="A9" s="101" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" s="7" customFormat="1" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" s="7" customFormat="1" ht="28.15" customHeight="1">
       <c r="A10" s="103" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.7">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" s="10" customFormat="1" ht="30">
       <c r="A11" s="100" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="27.6" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="27.6">
       <c r="A12" s="101" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" s="7" customFormat="1" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" s="7" customFormat="1" ht="28.15" customHeight="1">
       <c r="A13" s="103" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.7">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" s="10" customFormat="1" ht="30">
       <c r="A14" s="100" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="75" customHeight="1">
       <c r="A15" s="101" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="69" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="69">
       <c r="A16" s="101" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
       <c r="A17" s="104"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1">
       <c r="A18" s="104"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1">
       <c r="A19" s="104"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1">
       <c r="A20" s="104"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1">
       <c r="A21" s="104"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1">
       <c r="A22" s="104"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1">
       <c r="A23" s="104"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1">
       <c r="A24" s="104"/>
     </row>
   </sheetData>
@@ -5180,15 +5180,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="28" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="60f5a4f2d2b0abadcf532d48ebf9cb71">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7dd78129e6a1811f84807ad11c651531" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -5500,6 +5491,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -5521,51 +5521,15 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97245281-08F3-4104-84BD-39F3D8CFB195}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2348D59-3426-404A-A0C5-6456F6613EDB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2348D59-3426-404A-A0C5-6456F6613EDB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="16c05727-aa75-4e4a-9b5f-8a80a1165891"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97245281-08F3-4104-84BD-39F3D8CFB195}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A82239A0-E68C-493F-BEE6-C77FEA397FD6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-    <ds:schemaRef ds:uri="16c05727-aa75-4e4a-9b5f-8a80a1165891"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A82239A0-E68C-493F-BEE6-C77FEA397FD6}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
